--- a/tests/fixtures/sample_multisheet.xlsx
+++ b/tests/fixtures/sample_multisheet.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alpha" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beta" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gamma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Alpha" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Beta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gamma" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,14 +415,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Alpha sheet content</t>
-        </is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lorem</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ipsum dolor sit amet</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ipsum</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>日本語の説明文サンプル</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -436,14 +476,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Beta sheet content</t>
-        </is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Consectetur</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>adipiscing elit</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>English and 日本語 mixed sample</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -457,13 +537,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Gamma sheet content</t>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>サンプルA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lorem ipsum dolor sit amet consectetur</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>サンプルB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>日本語のテストデータです</t>
         </is>
       </c>
     </row>
